--- a/examples/STUDY01_TRAIL01/outputs/feedback/MW/MW_Ganesh.xlsx
+++ b/examples/STUDY01_TRAIL01/outputs/feedback/MW/MW_Ganesh.xlsx
@@ -15,12 +15,15 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Details" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Details!$A$3:$J$13</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
   <si>
     <t>pyCoreGage Report — MW</t>
   </si>
@@ -161,6 +164,39 @@
   </si>
   <si>
     <t>closed</t>
+  </si>
+  <si>
+    <t>chetan</t>
+  </si>
+  <si>
+    <t>not so good</t>
+  </si>
+  <si>
+    <t>yeah</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> wow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">so </t>
+  </si>
+  <si>
+    <t>ju</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what </t>
+  </si>
+  <si>
+    <t xml:space="preserve">you </t>
+  </si>
+  <si>
+    <t xml:space="preserve">are </t>
+  </si>
+  <si>
+    <t>doing</t>
+  </si>
+  <si>
+    <t>whY?</t>
   </si>
 </sst>
 </file>
@@ -758,8 +794,12 @@
       <c r="F5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="G5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
@@ -782,10 +822,18 @@
       <c r="F6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
+      <c r="G6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
@@ -806,10 +854,14 @@
       <c r="F7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="8"/>
+      <c r="G7" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="J7" s="6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -828,12 +880,20 @@
         <v>46135</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
@@ -856,7 +916,9 @@
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="I9" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -874,12 +936,20 @@
         <v>46135</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -900,7 +970,9 @@
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="I11" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -921,7 +993,9 @@
         <v>26</v>
       </c>
       <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
+      <c r="H12" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
@@ -942,7 +1016,9 @@
       <c r="F13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="8"/>
+      <c r="G13" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
